--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-26.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-26.xlsx
@@ -30328,7 +30328,7 @@
         <v>1816</v>
       </c>
       <c r="B11">
-        <v>11583</v>
+        <v>11588</v>
       </c>
     </row>
   </sheetData>

--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-26.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-07-26.xlsx
@@ -30328,7 +30328,7 @@
         <v>1816</v>
       </c>
       <c r="B11">
-        <v>11588</v>
+        <v>11590</v>
       </c>
     </row>
   </sheetData>
